--- a/Electrical/miniBCS-4_J005904.xlsx
+++ b/Electrical/miniBCS-4_J005904.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sawtelles\Documents\GitHub\miniBSC-4\Electrical\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C57F6CF-8BA7-4C58-9A36-0193E1BE2BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E0C213-35BC-4921-A31A-F7A5831E428F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6780" yWindow="615" windowWidth="30225" windowHeight="14250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="600" windowWidth="29490" windowHeight="14445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="J005904_miniBCSrevG" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="228">
   <si>
     <t>Qty</t>
   </si>
@@ -709,6 +709,15 @@
   </si>
   <si>
     <t>296-SN74LVC2G17DBVRCT-ND</t>
+  </si>
+  <si>
+    <t>J11</t>
+  </si>
+  <si>
+    <t>U2 U8</t>
+  </si>
+  <si>
+    <t>J26</t>
   </si>
 </sst>
 </file>
@@ -2808,6 +2817,9 @@
       <c r="C45" t="s">
         <v>175</v>
       </c>
+      <c r="D45" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="E45" s="1" t="s">
         <v>167</v>
       </c>
@@ -2835,6 +2847,9 @@
       <c r="C46" t="s">
         <v>209</v>
       </c>
+      <c r="D46" s="1" t="s">
+        <v>227</v>
+      </c>
       <c r="E46" s="1" t="s">
         <v>211</v>
       </c>
@@ -2862,6 +2877,9 @@
       <c r="C47" t="s">
         <v>216</v>
       </c>
+      <c r="D47" s="1" t="s">
+        <v>225</v>
+      </c>
       <c r="E47" s="1" t="s">
         <v>218</v>
       </c>
@@ -2888,6 +2906,9 @@
       </c>
       <c r="C48" t="s">
         <v>220</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>226</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>223</v>

--- a/Electrical/miniBCS-4_J005904.xlsx
+++ b/Electrical/miniBCS-4_J005904.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sawtelles\Documents\GitHub\miniBSC-4\Electrical\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E0C213-35BC-4921-A31A-F7A5831E428F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3962D0-B8EB-4233-88FE-25A3C53DF86A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="600" windowWidth="29490" windowHeight="14445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="J005904_miniBCSrevG" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="229">
   <si>
     <t>Qty</t>
   </si>
@@ -189,15 +189,9 @@
     <t>Murata</t>
   </si>
   <si>
-    <t>NDTD0515C</t>
-  </si>
-  <si>
     <t>DK</t>
   </si>
   <si>
-    <t>811-1370-5-ND</t>
-  </si>
-  <si>
     <t>THERMISTOR PTC 100 OHM SMD</t>
   </si>
   <si>
@@ -718,6 +712,15 @@
   </si>
   <si>
     <t>J26</t>
+  </si>
+  <si>
+    <t>TEN 3-0523N</t>
+  </si>
+  <si>
+    <t>TEN3-0523N-ND</t>
+  </si>
+  <si>
+    <t>Traco Power</t>
   </si>
 </sst>
 </file>
@@ -1585,7 +1588,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -1628,25 +1631,25 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" t="s">
         <v>58</v>
-      </c>
-      <c r="F4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H4" t="s">
-        <v>60</v>
       </c>
       <c r="I4" s="3">
         <v>0.5</v>
@@ -1661,7 +1664,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C5" t="s">
         <v>49</v>
@@ -1670,23 +1673,23 @@
         <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>50</v>
+        <v>228</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>226</v>
       </c>
       <c r="G5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H5" t="s">
-        <v>53</v>
+        <v>227</v>
       </c>
       <c r="I5" s="3">
-        <v>17.82</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="J5" s="3">
         <f t="shared" ref="J5" si="0">A5*I5</f>
-        <v>17.82</v>
+        <v>16.399999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -1694,25 +1697,25 @@
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6" t="s">
         <v>62</v>
-      </c>
-      <c r="F6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G6" t="s">
-        <v>52</v>
-      </c>
-      <c r="H6" t="s">
-        <v>64</v>
       </c>
       <c r="I6" s="3">
         <v>1.29</v>
@@ -1727,25 +1730,25 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" t="s">
         <v>159</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="G7" t="s">
-        <v>52</v>
-      </c>
-      <c r="H7" t="s">
-        <v>161</v>
       </c>
       <c r="I7" s="3">
         <v>1.17</v>
@@ -1763,22 +1766,22 @@
         <v>0.1</v>
       </c>
       <c r="C8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" t="s">
         <v>65</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" t="s">
         <v>66</v>
-      </c>
-      <c r="F8" t="s">
-        <v>67</v>
-      </c>
-      <c r="G8" t="s">
-        <v>52</v>
-      </c>
-      <c r="H8" t="s">
-        <v>68</v>
       </c>
       <c r="I8" s="3">
         <v>0.03</v>
@@ -1799,16 +1802,16 @@
         <v>17</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1819,22 +1822,22 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I10" s="3">
         <v>0.22</v>
@@ -1852,22 +1855,22 @@
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I11" s="3">
         <v>0.05</v>
@@ -1877,7 +1880,7 @@
         <v>0.1</v>
       </c>
       <c r="K11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1888,22 +1891,22 @@
         <v>22</v>
       </c>
       <c r="C12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" t="s">
         <v>82</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="E12" t="s">
-        <v>74</v>
-      </c>
-      <c r="F12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G12" t="s">
-        <v>52</v>
-      </c>
-      <c r="H12" t="s">
-        <v>84</v>
       </c>
       <c r="I12" s="3">
         <v>0.05</v>
@@ -1924,19 +1927,19 @@
         <v>20</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I13" s="3">
         <v>0.06</v>
@@ -1953,22 +1956,22 @@
         <v>24</v>
       </c>
       <c r="C14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E14" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14" t="s">
+        <v>51</v>
+      </c>
+      <c r="H14" t="s">
         <v>87</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="E14" t="s">
-        <v>74</v>
-      </c>
-      <c r="F14" t="s">
-        <v>88</v>
-      </c>
-      <c r="G14" t="s">
-        <v>52</v>
-      </c>
-      <c r="H14" t="s">
-        <v>89</v>
       </c>
       <c r="I14" s="3">
         <v>0.14000000000000001</v>
@@ -1986,22 +1989,22 @@
         <v>25</v>
       </c>
       <c r="C15" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" t="s">
+        <v>89</v>
+      </c>
+      <c r="G15" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15" t="s">
         <v>90</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E15" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" t="s">
-        <v>91</v>
-      </c>
-      <c r="G15" t="s">
-        <v>52</v>
-      </c>
-      <c r="H15" t="s">
-        <v>92</v>
       </c>
       <c r="I15" s="3">
         <v>0.51</v>
@@ -2016,25 +2019,25 @@
         <v>1</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F16" t="s">
+        <v>95</v>
+      </c>
+      <c r="G16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H16" t="s">
         <v>96</v>
-      </c>
-      <c r="F16" t="s">
-        <v>97</v>
-      </c>
-      <c r="G16" t="s">
-        <v>52</v>
-      </c>
-      <c r="H16" t="s">
-        <v>98</v>
       </c>
       <c r="I16" s="3">
         <v>0.37</v>
@@ -2052,22 +2055,22 @@
         <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E17" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" t="s">
         <v>100</v>
-      </c>
-      <c r="F17" t="s">
-        <v>101</v>
-      </c>
-      <c r="G17" t="s">
-        <v>52</v>
-      </c>
-      <c r="H17" t="s">
-        <v>102</v>
       </c>
       <c r="I17" s="3">
         <v>0.38</v>
@@ -2085,22 +2088,22 @@
         <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E18" t="s">
         <v>50</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H18" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I18" s="3">
         <v>0.45</v>
@@ -2121,13 +2124,13 @@
         <v>20</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>29</v>
       </c>
       <c r="G19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -2135,25 +2138,25 @@
         <v>3</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" t="s">
+        <v>102</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E20" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" t="s">
         <v>103</v>
       </c>
-      <c r="C20" t="s">
+      <c r="G20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H20" t="s">
         <v>104</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E20" t="s">
-        <v>74</v>
-      </c>
-      <c r="F20" t="s">
-        <v>105</v>
-      </c>
-      <c r="G20" t="s">
-        <v>52</v>
-      </c>
-      <c r="H20" t="s">
-        <v>106</v>
       </c>
       <c r="I20" s="3">
         <v>0.05</v>
@@ -2168,25 +2171,25 @@
         <v>1</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E21" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21" t="s">
+        <v>73</v>
+      </c>
+      <c r="G21" t="s">
+        <v>51</v>
+      </c>
+      <c r="H21" t="s">
         <v>74</v>
-      </c>
-      <c r="F21" t="s">
-        <v>75</v>
-      </c>
-      <c r="G21" t="s">
-        <v>52</v>
-      </c>
-      <c r="H21" t="s">
-        <v>76</v>
       </c>
       <c r="I21" s="3">
         <v>0.13</v>
@@ -2196,7 +2199,7 @@
         <v>0.13</v>
       </c>
       <c r="K21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -2207,22 +2210,22 @@
         <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E22" t="s">
+        <v>106</v>
+      </c>
+      <c r="F22" t="s">
+        <v>107</v>
+      </c>
+      <c r="G22" t="s">
+        <v>51</v>
+      </c>
+      <c r="H22" t="s">
         <v>108</v>
-      </c>
-      <c r="F22" t="s">
-        <v>109</v>
-      </c>
-      <c r="G22" t="s">
-        <v>52</v>
-      </c>
-      <c r="H22" t="s">
-        <v>110</v>
       </c>
       <c r="I22" s="3">
         <v>9.34</v>
@@ -2240,22 +2243,22 @@
         <v>33</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F23" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I23" s="3">
         <v>6.7</v>
@@ -2273,22 +2276,22 @@
         <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>36</v>
       </c>
       <c r="E24" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F24" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H24" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I24" s="3">
         <v>3.5</v>
@@ -2306,22 +2309,22 @@
         <v>37</v>
       </c>
       <c r="C25" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E25" t="s">
+        <v>116</v>
+      </c>
+      <c r="F25" t="s">
+        <v>117</v>
+      </c>
+      <c r="G25" t="s">
+        <v>51</v>
+      </c>
+      <c r="H25" t="s">
         <v>118</v>
-      </c>
-      <c r="F25" t="s">
-        <v>119</v>
-      </c>
-      <c r="G25" t="s">
-        <v>52</v>
-      </c>
-      <c r="H25" t="s">
-        <v>120</v>
       </c>
       <c r="I25" s="3">
         <v>2.4700000000000002</v>
@@ -2339,22 +2342,22 @@
         <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>40</v>
       </c>
       <c r="E26" t="s">
+        <v>120</v>
+      </c>
+      <c r="F26" t="s">
+        <v>121</v>
+      </c>
+      <c r="G26" t="s">
+        <v>51</v>
+      </c>
+      <c r="H26" t="s">
         <v>122</v>
-      </c>
-      <c r="F26" t="s">
-        <v>123</v>
-      </c>
-      <c r="G26" t="s">
-        <v>52</v>
-      </c>
-      <c r="H26" t="s">
-        <v>124</v>
       </c>
       <c r="I26" s="3">
         <v>10.75</v>
@@ -2372,22 +2375,22 @@
         <v>41</v>
       </c>
       <c r="C27" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F27" t="s">
+        <v>125</v>
+      </c>
+      <c r="G27" t="s">
+        <v>51</v>
+      </c>
+      <c r="H27" t="s">
         <v>126</v>
-      </c>
-      <c r="F27" t="s">
-        <v>127</v>
-      </c>
-      <c r="G27" t="s">
-        <v>52</v>
-      </c>
-      <c r="H27" t="s">
-        <v>128</v>
       </c>
       <c r="I27" s="3">
         <v>14.74</v>
@@ -2405,22 +2408,22 @@
         <v>43</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E28" t="s">
+        <v>128</v>
+      </c>
+      <c r="F28" t="s">
+        <v>129</v>
+      </c>
+      <c r="G28" t="s">
+        <v>51</v>
+      </c>
+      <c r="H28" t="s">
         <v>130</v>
-      </c>
-      <c r="F28" t="s">
-        <v>131</v>
-      </c>
-      <c r="G28" t="s">
-        <v>52</v>
-      </c>
-      <c r="H28" t="s">
-        <v>132</v>
       </c>
       <c r="I28" s="3">
         <v>1.46</v>
@@ -2438,22 +2441,22 @@
         <v>45</v>
       </c>
       <c r="C29" t="s">
+        <v>131</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29" t="s">
         <v>133</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="F29" t="s">
         <v>134</v>
       </c>
-      <c r="E29" t="s">
+      <c r="G29" t="s">
+        <v>51</v>
+      </c>
+      <c r="H29" t="s">
         <v>135</v>
-      </c>
-      <c r="F29" t="s">
-        <v>136</v>
-      </c>
-      <c r="G29" t="s">
-        <v>52</v>
-      </c>
-      <c r="H29" t="s">
-        <v>137</v>
       </c>
       <c r="I29" s="3">
         <v>4.6399999999999997</v>
@@ -2471,22 +2474,22 @@
         <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>48</v>
       </c>
       <c r="E30" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F30" t="s">
+        <v>202</v>
+      </c>
+      <c r="G30" t="s">
+        <v>51</v>
+      </c>
+      <c r="H30" t="s">
         <v>204</v>
-      </c>
-      <c r="G30" t="s">
-        <v>52</v>
-      </c>
-      <c r="H30" t="s">
-        <v>206</v>
       </c>
       <c r="I30" s="3">
         <v>0.87</v>
@@ -2501,25 +2504,25 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
+        <v>182</v>
+      </c>
+      <c r="C31" t="s">
         <v>184</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E31" t="s">
+        <v>185</v>
+      </c>
+      <c r="F31" t="s">
         <v>186</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="G31" t="s">
+        <v>51</v>
+      </c>
+      <c r="H31" t="s">
         <v>187</v>
-      </c>
-      <c r="F31" t="s">
-        <v>188</v>
-      </c>
-      <c r="G31" t="s">
-        <v>52</v>
-      </c>
-      <c r="H31" t="s">
-        <v>189</v>
       </c>
       <c r="I31" s="3">
         <v>0.43</v>
@@ -2540,25 +2543,25 @@
         <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C33" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F33" s="1">
         <v>1894804</v>
       </c>
       <c r="G33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H33" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I33" s="3">
         <v>2.67</v>
@@ -2573,22 +2576,22 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C34" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F34" s="1">
         <v>1881325</v>
       </c>
       <c r="G34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H34" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I34" s="3">
         <v>3.1</v>
@@ -2606,25 +2609,25 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
+        <v>145</v>
+      </c>
+      <c r="C36" t="s">
+        <v>144</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G36" t="s">
+        <v>51</v>
+      </c>
+      <c r="H36" t="s">
         <v>147</v>
-      </c>
-      <c r="C36" t="s">
-        <v>146</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="G36" t="s">
-        <v>52</v>
-      </c>
-      <c r="H36" t="s">
-        <v>149</v>
       </c>
       <c r="I36" s="3">
         <v>2.85</v>
@@ -2646,25 +2649,25 @@
         <v>9</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C38" t="s">
         <v>11</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E38" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F38" s="2">
         <v>112705</v>
       </c>
       <c r="G38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H38" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I38" s="3">
         <v>7.62</v>
@@ -2679,25 +2682,25 @@
         <v>7</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C39" t="s">
+        <v>137</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="F39" s="1">
         <v>432024101</v>
       </c>
       <c r="G39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H39" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I39" s="3">
         <v>1.54</v>
@@ -2718,22 +2721,22 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
+        <v>166</v>
+      </c>
+      <c r="C41" t="s">
+        <v>164</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C41" t="s">
-        <v>166</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="E41" s="1" t="s">
+      <c r="H41" t="s">
         <v>167</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="H41" t="s">
-        <v>169</v>
       </c>
       <c r="I41" s="3">
         <v>1.39</v>
@@ -2755,22 +2758,22 @@
         <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C43" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F43" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I43" s="3">
         <v>15</v>
@@ -2785,19 +2788,19 @@
         <v>4</v>
       </c>
       <c r="B44" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C44" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F44" s="1">
         <v>4848</v>
       </c>
       <c r="G44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H44" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I44" s="3">
         <v>1.05</v>
@@ -2812,22 +2815,22 @@
         <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C45" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H45" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I45" s="3">
         <v>4.8899999999999997</v>
@@ -2842,22 +2845,22 @@
         <v>1</v>
       </c>
       <c r="B46" t="s">
+        <v>208</v>
+      </c>
+      <c r="C46" t="s">
+        <v>207</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C46" t="s">
-        <v>209</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="E46" s="1" t="s">
+      <c r="H46" t="s">
         <v>211</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="H46" t="s">
-        <v>213</v>
       </c>
       <c r="I46" s="3">
         <v>1.01</v>
@@ -2872,22 +2875,22 @@
         <v>1</v>
       </c>
       <c r="B47" t="s">
+        <v>213</v>
+      </c>
+      <c r="C47" t="s">
+        <v>214</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C47" t="s">
-        <v>216</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F47" s="1" t="s">
+      <c r="H47" t="s">
         <v>217</v>
-      </c>
-      <c r="H47" t="s">
-        <v>219</v>
       </c>
       <c r="I47" s="3">
         <v>0.6</v>
@@ -2902,22 +2905,22 @@
         <v>2</v>
       </c>
       <c r="B48" t="s">
+        <v>219</v>
+      </c>
+      <c r="C48" t="s">
+        <v>218</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C48" t="s">
+      <c r="F48" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F48" s="1" t="s">
+      <c r="H48" t="s">
         <v>222</v>
-      </c>
-      <c r="H48" t="s">
-        <v>224</v>
       </c>
       <c r="I48" s="3">
         <v>0.4</v>
@@ -2932,13 +2935,13 @@
         <v>1</v>
       </c>
       <c r="B50" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I50" s="3">
         <v>21.98</v>
@@ -2953,13 +2956,13 @@
         <v>2</v>
       </c>
       <c r="B51" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I51" s="3">
         <v>1.35</v>
@@ -2972,7 +2975,7 @@
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="J56" s="3">
         <f>SUM(J4:J52)</f>
-        <v>282.41000000000003</v>
+        <v>280.99</v>
       </c>
     </row>
   </sheetData>
